--- a/output/docs/DOC_040_traceability.xlsx
+++ b/output/docs/DOC_040_traceability.xlsx
@@ -478,7 +478,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -976,54 +976,54 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>FND-0009</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
-        <is>
-          <t>SCA</t>
-        </is>
-      </c>
-      <c r="C13" s="5" t="inlineStr">
-        <is>
-          <t>DOC_071</t>
-        </is>
-      </c>
-      <c r="D13" s="5" t="inlineStr">
-        <is>
-          <t>CVE-2099-0101</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>DAST</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>DOC_069</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>CWE-639</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>RCM-FND-0009</t>
         </is>
       </c>
-      <c r="F13" s="5" t="inlineStr">
+      <c r="F13" s="6" t="inlineStr">
         <is>
           <t>TST-FND-0009</t>
         </is>
       </c>
-      <c r="G13" s="5" t="inlineStr">
-        <is>
-          <t>FAIL/OPEN</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>SRSK-VT-0001</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Applicable</t>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H13" s="6" t="inlineStr">
+        <is>
+          <t>SRSK-DAST-0001</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
     </row>
@@ -1035,17 +1035,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>SCA</t>
+          <t>DAST</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>DOC_071</t>
+          <t>DOC_069</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>CVE-2099-0102</t>
+          <t>CWE-306</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -1065,7 +1065,7 @@
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>SRSK-VT-0002</t>
+          <t>SRSK-DAST-0002</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
@@ -1080,54 +1080,54 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>FND-0011</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>DAST</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>DOC_069</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>CWE-639</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>CWE-20</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>RCM-FND-0011</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>TST-FND-0011</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
-        <is>
-          <t>FAIL/OPEN</t>
-        </is>
-      </c>
-      <c r="H15" s="6" t="inlineStr">
-        <is>
-          <t>SRSK-DAST-0001</t>
-        </is>
-      </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="G15" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H15" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-DAST-0003</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
         </is>
       </c>
     </row>
@@ -1149,7 +1149,7 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>CWE-306</t>
+          <t>CWE-20</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>SRSK-DAST-0002</t>
+          <t>SRSK-DAST-0004</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
@@ -1201,325 +1201,321 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
+          <t>CWE-190</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>RCM-FND-0013</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>TST-FND-0013</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>SRSK-FUZZ-0001</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>FND-0014</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FUZZ</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>DOC_066</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
           <t>CWE-20</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>RCM-FND-0013</t>
-        </is>
-      </c>
-      <c r="F17" s="4" t="inlineStr">
-        <is>
-          <t>TST-FND-0013</t>
-        </is>
-      </c>
-      <c r="G17" s="4" t="inlineStr">
-        <is>
-          <t>FAIL/OPEN</t>
-        </is>
-      </c>
-      <c r="H17" s="4" t="inlineStr">
-        <is>
-          <t>SRSK-FUZZ-0001</t>
-        </is>
-      </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>RCM-FND-0014</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>TST-FND-0014</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>SRSK-FUZZ-0002</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
         <is>
           <t>Low</t>
         </is>
       </c>
-      <c r="J17" s="4" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
-        <is>
-          <t>FND-0014</t>
-        </is>
-      </c>
-      <c r="B18" s="5" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>FND-0015</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>ASA</t>
         </is>
       </c>
-      <c r="C18" s="5" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>DOC_067</t>
         </is>
       </c>
-      <c r="D18" s="5" t="inlineStr">
-        <is>
-          <t>CWE-200</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr">
-        <is>
-          <t>RCM-FND-0014</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>TST-FND-0014</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr">
-        <is>
-          <t>FAIL/OPEN</t>
-        </is>
-      </c>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>CWE-693</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0015</t>
+        </is>
+      </c>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0015</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H19" s="5" t="inlineStr">
         <is>
           <t>SRSK-ASA-0001</t>
         </is>
       </c>
-      <c r="I18" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J18" s="5" t="inlineStr">
-        <is>
-          <t>Applicable</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>CTRL-SSH-001</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>COMPLIANCE</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr"/>
-      <c r="D19" s="7" t="inlineStr">
-        <is>
-          <t>CWE-327</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>RCM-CTRL-SSH-001</t>
-        </is>
-      </c>
-      <c r="F19" s="7" t="inlineStr">
-        <is>
-          <t>TST-CTRL-SSH-001</t>
-        </is>
-      </c>
-      <c r="G19" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H19" s="7" t="inlineStr">
-        <is>
-          <t>N/A (verified)</t>
-        </is>
-      </c>
-      <c r="I19" s="7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J19" s="7" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>FND-0016</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>DOC_067</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>CWE-319</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>RCM-FND-0016</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>TST-FND-0016</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>SRSK-ASA-0002</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>SRT-001</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>SRT</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>DOC_036</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="inlineStr">
-        <is>
-          <t>CWE-327</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>RCM-SRT-001</t>
-        </is>
-      </c>
-      <c r="F20" s="7" t="inlineStr">
-        <is>
-          <t>SRT-001</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H20" s="7" t="inlineStr">
-        <is>
-          <t>N/A (verified)</t>
-        </is>
-      </c>
-      <c r="I20" s="7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J20" s="7" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>FND-0017</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>ASA</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>DOC_067</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="inlineStr">
+        <is>
+          <t>CWE-693</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>RCM-FND-0017</t>
+        </is>
+      </c>
+      <c r="F21" s="4" t="inlineStr">
+        <is>
+          <t>TST-FND-0017</t>
+        </is>
+      </c>
+      <c r="G21" s="4" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>SRSK-ASA-0003</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>SRT-002</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>SRT</t>
-        </is>
-      </c>
-      <c r="C21" s="7" t="inlineStr">
-        <is>
-          <t>DOC_036</t>
-        </is>
-      </c>
-      <c r="D21" s="7" t="inlineStr">
-        <is>
-          <t>CWE-311</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>RCM-SRT-002</t>
-        </is>
-      </c>
-      <c r="F21" s="7" t="inlineStr">
-        <is>
-          <t>SRT-002</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H21" s="7" t="inlineStr">
-        <is>
-          <t>N/A (verified)</t>
-        </is>
-      </c>
-      <c r="I21" s="7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-    </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t>SRT-003</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="inlineStr">
-        <is>
-          <t>SRT</t>
-        </is>
-      </c>
-      <c r="C22" s="7" t="inlineStr">
-        <is>
-          <t>DOC_036</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="inlineStr">
-        <is>
-          <t>CWE-732</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>RCM-SRT-003</t>
-        </is>
-      </c>
-      <c r="F22" s="7" t="inlineStr">
-        <is>
-          <t>SRT-003</t>
-        </is>
-      </c>
-      <c r="G22" s="7" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>N/A (verified)</t>
-        </is>
-      </c>
-      <c r="I22" s="7" t="inlineStr">
-        <is>
-          <t>Verified</t>
-        </is>
-      </c>
-      <c r="J22" s="7" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>FND-0018</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr"/>
+      <c r="E22" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0018</t>
+        </is>
+      </c>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0018</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H22" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0001</t>
+        </is>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>FND-0019</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>TMT</t>
+          <t>SCA</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>DOC_035</t>
-        </is>
-      </c>
-      <c r="D23" s="5" t="inlineStr">
-        <is>
-          <t>CWE-311</t>
-        </is>
-      </c>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr"/>
       <c r="E23" s="5" t="inlineStr">
         <is>
-          <t>RCM-TMT-001</t>
+          <t>RCM-FND-0019</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>TMT-001</t>
+          <t>TST-FND-0019</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -1529,7 +1525,7 @@
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>SRSK-CT-0001</t>
+          <t>SRSK-VT-0002</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
@@ -1546,50 +1542,2226 @@
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
         <is>
+          <t>FND-0020</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr"/>
+      <c r="E24" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0020</t>
+        </is>
+      </c>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0020</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H24" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0003</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>FND-0021</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0021</t>
+        </is>
+      </c>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0021</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H25" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0004</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>FND-0022</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr"/>
+      <c r="E26" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0022</t>
+        </is>
+      </c>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0022</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H26" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0005</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>FND-0023</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr"/>
+      <c r="E27" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0023</t>
+        </is>
+      </c>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0023</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H27" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0006</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>FND-0024</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr"/>
+      <c r="E28" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0024</t>
+        </is>
+      </c>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0024</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H28" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0007</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>FND-0025</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr"/>
+      <c r="E29" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0025</t>
+        </is>
+      </c>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0025</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H29" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0008</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>FND-0026</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0026</t>
+        </is>
+      </c>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0026</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H30" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0009</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>FND-0027</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr"/>
+      <c r="E31" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0027</t>
+        </is>
+      </c>
+      <c r="F31" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0027</t>
+        </is>
+      </c>
+      <c r="G31" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H31" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0010</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>FND-0028</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr"/>
+      <c r="E32" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0028</t>
+        </is>
+      </c>
+      <c r="F32" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0028</t>
+        </is>
+      </c>
+      <c r="G32" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H32" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0011</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="inlineStr">
+        <is>
+          <t>FND-0029</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr"/>
+      <c r="E33" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0029</t>
+        </is>
+      </c>
+      <c r="F33" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0029</t>
+        </is>
+      </c>
+      <c r="G33" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H33" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0012</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>FND-0030</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr"/>
+      <c r="E34" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0030</t>
+        </is>
+      </c>
+      <c r="F34" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0030</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0013</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="inlineStr">
+        <is>
+          <t>FND-0031</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr"/>
+      <c r="E35" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0031</t>
+        </is>
+      </c>
+      <c r="F35" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0031</t>
+        </is>
+      </c>
+      <c r="G35" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H35" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0014</t>
+        </is>
+      </c>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>FND-0032</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr"/>
+      <c r="E36" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0032</t>
+        </is>
+      </c>
+      <c r="F36" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0032</t>
+        </is>
+      </c>
+      <c r="G36" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H36" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0015</t>
+        </is>
+      </c>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>FND-0033</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0033</t>
+        </is>
+      </c>
+      <c r="F37" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0033</t>
+        </is>
+      </c>
+      <c r="G37" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H37" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0016</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="inlineStr">
+        <is>
+          <t>FND-0034</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr"/>
+      <c r="E38" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0034</t>
+        </is>
+      </c>
+      <c r="F38" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0034</t>
+        </is>
+      </c>
+      <c r="G38" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0017</t>
+        </is>
+      </c>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="inlineStr">
+        <is>
+          <t>FND-0035</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0035</t>
+        </is>
+      </c>
+      <c r="F39" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0035</t>
+        </is>
+      </c>
+      <c r="G39" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H39" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0018</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>FND-0036</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0036</t>
+        </is>
+      </c>
+      <c r="F40" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0036</t>
+        </is>
+      </c>
+      <c r="G40" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H40" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0019</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
+        <is>
+          <t>FND-0037</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0037</t>
+        </is>
+      </c>
+      <c r="F41" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0037</t>
+        </is>
+      </c>
+      <c r="G41" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H41" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0020</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>FND-0038</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr"/>
+      <c r="E42" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0038</t>
+        </is>
+      </c>
+      <c r="F42" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0038</t>
+        </is>
+      </c>
+      <c r="G42" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0021</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>FND-0039</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0039</t>
+        </is>
+      </c>
+      <c r="F43" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0039</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0022</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>FND-0040</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0040</t>
+        </is>
+      </c>
+      <c r="F44" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0040</t>
+        </is>
+      </c>
+      <c r="G44" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H44" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0023</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>FND-0041</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr"/>
+      <c r="E45" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0041</t>
+        </is>
+      </c>
+      <c r="F45" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0041</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H45" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0024</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>FND-0042</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0042</t>
+        </is>
+      </c>
+      <c r="F46" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0042</t>
+        </is>
+      </c>
+      <c r="G46" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H46" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0025</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
+        <is>
+          <t>FND-0043</t>
+        </is>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0043</t>
+        </is>
+      </c>
+      <c r="F47" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0043</t>
+        </is>
+      </c>
+      <c r="G47" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H47" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0026</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>FND-0044</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C48" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D48" s="5" t="inlineStr"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0044</t>
+        </is>
+      </c>
+      <c r="F48" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0044</t>
+        </is>
+      </c>
+      <c r="G48" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H48" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0027</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>FND-0045</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C49" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D49" s="5" t="inlineStr"/>
+      <c r="E49" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0045</t>
+        </is>
+      </c>
+      <c r="F49" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0045</t>
+        </is>
+      </c>
+      <c r="G49" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H49" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0028</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J49" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="5" t="inlineStr">
+        <is>
+          <t>FND-0046</t>
+        </is>
+      </c>
+      <c r="B50" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C50" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0046</t>
+        </is>
+      </c>
+      <c r="F50" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0046</t>
+        </is>
+      </c>
+      <c r="G50" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H50" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0029</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="5" t="inlineStr">
+        <is>
+          <t>FND-0047</t>
+        </is>
+      </c>
+      <c r="B51" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C51" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D51" s="5" t="inlineStr"/>
+      <c r="E51" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0047</t>
+        </is>
+      </c>
+      <c r="F51" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0047</t>
+        </is>
+      </c>
+      <c r="G51" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H51" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0030</t>
+        </is>
+      </c>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>FND-0048</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0048</t>
+        </is>
+      </c>
+      <c r="F52" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0048</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0031</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t>FND-0049</t>
+        </is>
+      </c>
+      <c r="B53" s="5" t="inlineStr">
+        <is>
+          <t>SCA</t>
+        </is>
+      </c>
+      <c r="C53" s="5" t="inlineStr">
+        <is>
+          <t>DOC_071</t>
+        </is>
+      </c>
+      <c r="D53" s="5" t="inlineStr"/>
+      <c r="E53" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0049</t>
+        </is>
+      </c>
+      <c r="F53" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0049</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-VT-0032</t>
+        </is>
+      </c>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t>FND-0050</t>
+        </is>
+      </c>
+      <c r="B54" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C54" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0050</t>
+        </is>
+      </c>
+      <c r="F54" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0050</t>
+        </is>
+      </c>
+      <c r="G54" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0001</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="5" t="inlineStr">
+        <is>
+          <t>FND-0051</t>
+        </is>
+      </c>
+      <c r="B55" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C55" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0051</t>
+        </is>
+      </c>
+      <c r="F55" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0051</t>
+        </is>
+      </c>
+      <c r="G55" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H55" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0002</t>
+        </is>
+      </c>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="5" t="inlineStr">
+        <is>
+          <t>FND-0052</t>
+        </is>
+      </c>
+      <c r="B56" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C56" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D56" s="5" t="inlineStr"/>
+      <c r="E56" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0052</t>
+        </is>
+      </c>
+      <c r="F56" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0052</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H56" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0003</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
+        <is>
+          <t>FND-0053</t>
+        </is>
+      </c>
+      <c r="B57" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C57" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D57" s="5" t="inlineStr"/>
+      <c r="E57" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0053</t>
+        </is>
+      </c>
+      <c r="F57" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0053</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H57" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0004</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="5" t="inlineStr">
+        <is>
+          <t>FND-0054</t>
+        </is>
+      </c>
+      <c r="B58" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C58" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D58" s="5" t="inlineStr"/>
+      <c r="E58" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0054</t>
+        </is>
+      </c>
+      <c r="F58" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0054</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H58" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0005</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>FND-0055</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C59" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0055</t>
+        </is>
+      </c>
+      <c r="F59" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0055</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H59" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0006</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="5" t="inlineStr">
+        <is>
+          <t>FND-0056</t>
+        </is>
+      </c>
+      <c r="B60" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C60" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D60" s="5" t="inlineStr"/>
+      <c r="E60" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0056</t>
+        </is>
+      </c>
+      <c r="F60" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0056</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H60" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0007</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="5" t="inlineStr">
+        <is>
+          <t>FND-0057</t>
+        </is>
+      </c>
+      <c r="B61" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C61" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0057</t>
+        </is>
+      </c>
+      <c r="F61" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0057</t>
+        </is>
+      </c>
+      <c r="G61" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H61" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0008</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="5" t="inlineStr">
+        <is>
+          <t>FND-0058</t>
+        </is>
+      </c>
+      <c r="B62" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C62" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0058</t>
+        </is>
+      </c>
+      <c r="F62" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0058</t>
+        </is>
+      </c>
+      <c r="G62" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H62" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0009</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="5" t="inlineStr">
+        <is>
+          <t>FND-0059</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0059</t>
+        </is>
+      </c>
+      <c r="F63" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0059</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0010</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>FND-0060</t>
+        </is>
+      </c>
+      <c r="B64" s="5" t="inlineStr">
+        <is>
+          <t>CBT</t>
+        </is>
+      </c>
+      <c r="C64" s="5" t="inlineStr">
+        <is>
+          <t>DOC_070</t>
+        </is>
+      </c>
+      <c r="D64" s="5" t="inlineStr"/>
+      <c r="E64" s="5" t="inlineStr">
+        <is>
+          <t>RCM-FND-0060</t>
+        </is>
+      </c>
+      <c r="F64" s="5" t="inlineStr">
+        <is>
+          <t>TST-FND-0060</t>
+        </is>
+      </c>
+      <c r="G64" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H64" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CBT-0011</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="7" t="inlineStr">
+        <is>
+          <t>SRT-001</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>SRT</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>DOC_036</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>CWE-327</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>RCM-SRT-001</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>SRT-001</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>N/A (verified)</t>
+        </is>
+      </c>
+      <c r="I65" s="7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J65" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="7" t="inlineStr">
+        <is>
+          <t>SRT-002</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>SRT</t>
+        </is>
+      </c>
+      <c r="C66" s="7" t="inlineStr">
+        <is>
+          <t>DOC_036</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>CWE-311</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>RCM-SRT-002</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>SRT-002</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H66" s="7" t="inlineStr">
+        <is>
+          <t>N/A (verified)</t>
+        </is>
+      </c>
+      <c r="I66" s="7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J66" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="7" t="inlineStr">
+        <is>
+          <t>SRT-003</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>SRT</t>
+        </is>
+      </c>
+      <c r="C67" s="7" t="inlineStr">
+        <is>
+          <t>DOC_036</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>CWE-732</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>RCM-SRT-003</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>SRT-003</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>N/A (verified)</t>
+        </is>
+      </c>
+      <c r="I67" s="7" t="inlineStr">
+        <is>
+          <t>Verified</t>
+        </is>
+      </c>
+      <c r="J67" s="7" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>TMT</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>DOC_035</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>CWE-311</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="inlineStr">
+        <is>
+          <t>RCM-TMT-001</t>
+        </is>
+      </c>
+      <c r="F68" s="5" t="inlineStr">
+        <is>
+          <t>TMT-001</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H68" s="5" t="inlineStr">
+        <is>
+          <t>SRSK-CT-0001</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Applicable</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
           <t>TMT-002</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B69" s="5" t="inlineStr">
         <is>
           <t>TMT</t>
         </is>
       </c>
-      <c r="C24" s="5" t="inlineStr">
+      <c r="C69" s="5" t="inlineStr">
         <is>
           <t>DOC_035</t>
         </is>
       </c>
-      <c r="D24" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>CWE-778</t>
         </is>
       </c>
-      <c r="E24" s="5" t="inlineStr">
+      <c r="E69" s="5" t="inlineStr">
         <is>
           <t>RCM-TMT-002</t>
         </is>
       </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="F69" s="5" t="inlineStr">
         <is>
           <t>TMT-002</t>
         </is>
       </c>
-      <c r="G24" s="5" t="inlineStr">
-        <is>
-          <t>FAIL/OPEN</t>
-        </is>
-      </c>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
+        <is>
+          <t>FAIL/OPEN</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
         <is>
           <t>SRSK-CT-0002</t>
         </is>
       </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="I69" s="5" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
         <is>
           <t>Applicable</t>
         </is>
